--- a/Cobra_demo - Copy/data file log.xlsx
+++ b/Cobra_demo - Copy/data file log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\chrono_workspace\py_space\Cobra_demo - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76709B0-02FC-4F33-9A31-95A72E0BE54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1565B5-DF60-43BF-BD82-B2F28883695C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1890" yWindow="7980" windowWidth="25605" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>data file name</t>
   </si>
@@ -52,12 +52,18 @@
   </si>
   <si>
     <t>RTF around 1200. No visualizer was used</t>
+  </si>
+  <si>
+    <t>output_04_2_sand_steer_curve.csv</t>
+  </si>
+  <si>
+    <t>redo of previous sim, but steering set to 10 deg (previous was 20) to avoid skid</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -110,7 +116,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{8FE27DC6-2C84-499D-A250-7F31BF90136B}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -434,15 +442,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="C1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="50.6328125" customWidth="1"/>
-    <col min="4" max="4" width="75.6328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="50.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="50.5703125" customWidth="1"/>
+    <col min="4" max="4" width="75.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="50.5703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:5" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="3:5" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="3:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:5" ht="30" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>1</v>
       </c>
@@ -464,7 +472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="3:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:5" ht="30" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>2</v>
       </c>
@@ -473,6 +481,14 @@
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Cobra_demo - Copy/data file log.xlsx
+++ b/Cobra_demo - Copy/data file log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\chrono_workspace\py_space\Cobra_demo - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1565B5-DF60-43BF-BD82-B2F28883695C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DEF93E-008F-4CDD-9D05-FCB5689D9CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="7980" windowWidth="25605" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="2440" windowWidth="20000" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,39 +25,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>data file name</t>
   </si>
   <si>
-    <t>output_02_2_test_clay.csv</t>
-  </si>
-  <si>
-    <t>output_04_sand_steer_curve.csv</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
-    <t>Fine terrain mesh test. Straight line, clay params. Mesh size = 0.0025m (2.5mm). Usually 0.01m (10mm). RTF around 1200. Will compare to 0.01 mesh size</t>
-  </si>
-  <si>
-    <t>Mesh of 0.01. RTF about 120. Added steering motor torque output. Will use to calculate servo motor torque/motor spec required</t>
-  </si>
-  <si>
     <t>Sim Note</t>
   </si>
   <si>
-    <t>RTF ~120. Do to the velocity of the wheels and steering angle, vehicle performed more of a skid</t>
-  </si>
-  <si>
-    <t>RTF around 1200. No visualizer was used</t>
-  </si>
-  <si>
-    <t>output_04_2_sand_steer_curve.csv</t>
-  </si>
-  <si>
-    <t>redo of previous sim, but steering set to 10 deg (previous was 20) to avoid skid</t>
+    <t>output_01_straight5s_50rpm_Clay_Soil.csv</t>
+  </si>
+  <si>
+    <t>output_01_straight5s_50rpm_Sand_Soil.csv</t>
+  </si>
+  <si>
+    <t>soil mesh size of 10mm</t>
+  </si>
+  <si>
+    <t>RTF~150, due to mesh size, there is a drift when encountering the grid ((negligible)</t>
+  </si>
+  <si>
+    <t>output_02_straight5s_50rpm_Sand_Soil_fine</t>
+  </si>
+  <si>
+    <t>scm mesh size of 2.5mm</t>
+  </si>
+  <si>
+    <t>Avg RTF~1317.74</t>
+  </si>
+  <si>
+    <t>output_03_curve_20deg_5s_50rpm_Sand.csv</t>
+  </si>
+  <si>
+    <t>scm mesh size of 10mm, steering at 20deg</t>
   </si>
 </sst>
 </file>
@@ -136,21 +139,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>463550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>179299</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>118976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01F11CC0-9CA1-41DE-8072-0D5B477F2E51}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A608B014-3511-0D08-A791-8C173944DCD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -166,8 +169,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13576300" y="558800"/>
-          <a:ext cx="2292350" cy="1100049"/>
+          <a:off x="13557250" y="190500"/>
+          <a:ext cx="1212850" cy="855576"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -442,53 +445,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="50.5703125" customWidth="1"/>
-    <col min="4" max="4" width="75.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="50.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="50.54296875" customWidth="1"/>
+    <col min="4" max="4" width="75.54296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="50.54296875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:5" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:5" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="3:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="3:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="3" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
         <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="3:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3" t="s">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
         <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
